--- a/data/deliverables/weekly_report.xlsx
+++ b/data/deliverables/weekly_report.xlsx
@@ -2181,7 +2181,7 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>核验时间: 2026-09-17 22:00:49 | 结论: 全部通过 PASS</t>
+          <t>核验时间: 2026-09-18 22:18:26 | 结论: 全部通过 PASS</t>
         </is>
       </c>
     </row>
